--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/84.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/84.xlsx
@@ -426,13 +426,13 @@
         <v>-12.03951656941897</v>
       </c>
       <c r="E2">
-        <v>-17.92124776615472</v>
+        <v>-18.87844037410402</v>
       </c>
       <c r="F2">
-        <v>-0.07250824480885132</v>
+        <v>-0.5305191629657704</v>
       </c>
       <c r="G2">
-        <v>-12.82156856535206</v>
+        <v>-14.36362895390843</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.79630139833843</v>
       </c>
       <c r="E3">
-        <v>-17.90475959229279</v>
+        <v>-17.5865437237738</v>
       </c>
       <c r="F3">
-        <v>-0.5862260185413529</v>
+        <v>-1.073134818537296</v>
       </c>
       <c r="G3">
-        <v>-11.96224363863236</v>
+        <v>-12.0974297657285</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.411332977947476</v>
       </c>
       <c r="E4">
-        <v>-18.22260412594316</v>
+        <v>-19.9180421520449</v>
       </c>
       <c r="F4">
-        <v>0.1904566202143763</v>
+        <v>-1.352156877837164</v>
       </c>
       <c r="G4">
-        <v>-11.81874804223265</v>
+        <v>-14.70886257438024</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.028683024148101</v>
       </c>
       <c r="E5">
-        <v>-18.55006713838582</v>
+        <v>-19.60624313119477</v>
       </c>
       <c r="F5">
-        <v>0.2564195552983447</v>
+        <v>-1.008945634078619</v>
       </c>
       <c r="G5">
-        <v>-12.3373383798684</v>
+        <v>-14.04203924967809</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.661023203117296</v>
       </c>
       <c r="E6">
-        <v>-19.16461728901875</v>
+        <v>-20.6725538488329</v>
       </c>
       <c r="F6">
-        <v>0.3409070984752083</v>
+        <v>-1.237143403140205</v>
       </c>
       <c r="G6">
-        <v>-10.83510550942224</v>
+        <v>-13.44475889984663</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.350091300415536</v>
       </c>
       <c r="E7">
-        <v>-19.76922743920484</v>
+        <v>-20.22212918165997</v>
       </c>
       <c r="F7">
-        <v>0.5400193165467906</v>
+        <v>-0.7082275955901886</v>
       </c>
       <c r="G7">
-        <v>-11.35378192124201</v>
+        <v>-12.59967594003687</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.100214335291446</v>
       </c>
       <c r="E8">
-        <v>-21.12502991473131</v>
+        <v>-22.38691183933869</v>
       </c>
       <c r="F8">
-        <v>0.3801172813826159</v>
+        <v>-0.6464179292694601</v>
       </c>
       <c r="G8">
-        <v>-12.1102349558744</v>
+        <v>-11.99089309972921</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.938427013225147</v>
       </c>
       <c r="E9">
-        <v>-22.48074182077762</v>
+        <v>-21.58102913340768</v>
       </c>
       <c r="F9">
-        <v>0.4285248363939381</v>
+        <v>-0.2366031413841519</v>
       </c>
       <c r="G9">
-        <v>-10.83797575240479</v>
+        <v>-11.6989460202575</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.852661597862101</v>
       </c>
       <c r="E10">
-        <v>-21.2641219938769</v>
+        <v>-22.83351900292315</v>
       </c>
       <c r="F10">
-        <v>0.9368857248674658</v>
+        <v>0.1908525466932361</v>
       </c>
       <c r="G10">
-        <v>-10.09401671663761</v>
+        <v>-10.2139908869808</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.8542519186295768</v>
       </c>
       <c r="E11">
-        <v>-22.51324267873067</v>
+        <v>-23.12269376763096</v>
       </c>
       <c r="F11">
-        <v>1.28193406748792</v>
+        <v>-0.196198844216503</v>
       </c>
       <c r="G11">
-        <v>-9.137179671058675</v>
+        <v>-9.388016396023712</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.06364654409728496</v>
       </c>
       <c r="E12">
-        <v>-22.12196441057192</v>
+        <v>-24.91562078216983</v>
       </c>
       <c r="F12">
-        <v>1.02289045831132</v>
+        <v>0.4013492347379549</v>
       </c>
       <c r="G12">
-        <v>-9.136752610684107</v>
+        <v>-10.02015844565647</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.9154921906109231</v>
       </c>
       <c r="E13">
-        <v>-23.45695854803314</v>
+        <v>-24.88783859413277</v>
       </c>
       <c r="F13">
-        <v>1.373925209292136</v>
+        <v>-0.09909787527612192</v>
       </c>
       <c r="G13">
-        <v>-8.437671330247291</v>
+        <v>-9.679294745296488</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.697005316916665</v>
       </c>
       <c r="E14">
-        <v>-25.74618819991665</v>
+        <v>-26.1660411390638</v>
       </c>
       <c r="F14">
-        <v>1.38588694007145</v>
+        <v>-0.1079903839913144</v>
       </c>
       <c r="G14">
-        <v>-8.72493067723539</v>
+        <v>-9.873342372080868</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.428426102528536</v>
       </c>
       <c r="E15">
-        <v>-25.21692280027018</v>
+        <v>-27.32465574240027</v>
       </c>
       <c r="F15">
-        <v>1.720555674122114</v>
+        <v>0.00948258599232204</v>
       </c>
       <c r="G15">
-        <v>-7.354656151984575</v>
+        <v>-7.746644607107519</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.114570122050324</v>
       </c>
       <c r="E16">
-        <v>-26.89146644730053</v>
+        <v>-27.34654185727934</v>
       </c>
       <c r="F16">
-        <v>2.158113030381132</v>
+        <v>0.7437860463038494</v>
       </c>
       <c r="G16">
-        <v>-7.236562371507693</v>
+        <v>-7.63476141006231</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.758903355803991</v>
       </c>
       <c r="E17">
-        <v>-26.62478461298883</v>
+        <v>-28.88684342082631</v>
       </c>
       <c r="F17">
-        <v>1.902694524044974</v>
+        <v>0.6678631847176822</v>
       </c>
       <c r="G17">
-        <v>-7.135713222744875</v>
+        <v>-6.89249075252016</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.366675901157929</v>
       </c>
       <c r="E18">
-        <v>-27.33589994336132</v>
+        <v>-28.10055089345249</v>
       </c>
       <c r="F18">
-        <v>1.823867145809891</v>
+        <v>0.6942271370920028</v>
       </c>
       <c r="G18">
-        <v>-5.821880188393093</v>
+        <v>-7.32115674167269</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.921220404219167</v>
       </c>
       <c r="E19">
-        <v>-29.33625370982153</v>
+        <v>-29.04944280854572</v>
       </c>
       <c r="F19">
-        <v>1.869800952181297</v>
+        <v>0.5422491744757294</v>
       </c>
       <c r="G19">
-        <v>-5.74499276824352</v>
+        <v>-8.871978488998739</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.412142001988505</v>
       </c>
       <c r="E20">
-        <v>-30.2854014836962</v>
+        <v>-31.15004566835074</v>
       </c>
       <c r="F20">
-        <v>2.210646139302174</v>
+        <v>1.408123754830135</v>
       </c>
       <c r="G20">
-        <v>-5.006032656240642</v>
+        <v>-6.744952980017</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.819027202010043</v>
       </c>
       <c r="E21">
-        <v>-30.48915337896032</v>
+        <v>-31.73378634607248</v>
       </c>
       <c r="F21">
-        <v>2.26313965557533</v>
+        <v>1.282341079908188</v>
       </c>
       <c r="G21">
-        <v>-4.76824279124587</v>
+        <v>-5.465089453443681</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.120520219696755</v>
       </c>
       <c r="E22">
-        <v>-31.2338564010477</v>
+        <v>-31.70692343825898</v>
       </c>
       <c r="F22">
-        <v>1.692368876239123</v>
+        <v>0.7314473935166607</v>
       </c>
       <c r="G22">
-        <v>-5.11864748385003</v>
+        <v>-5.45600531648392</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.302855317757663</v>
       </c>
       <c r="E23">
-        <v>-31.53534861505637</v>
+        <v>-31.35694711728719</v>
       </c>
       <c r="F23">
-        <v>1.871033075383508</v>
+        <v>1.492018991994625</v>
       </c>
       <c r="G23">
-        <v>-4.165726813644054</v>
+        <v>-5.624277035699536</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>6.354570754537813</v>
       </c>
       <c r="E24">
-        <v>-30.43096701643576</v>
+        <v>-33.59393629301822</v>
       </c>
       <c r="F24">
-        <v>2.476930451924163</v>
+        <v>0.918009534061343</v>
       </c>
       <c r="G24">
-        <v>-4.083214776623259</v>
+        <v>-5.53945092734679</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.275671228947333</v>
       </c>
       <c r="E25">
-        <v>-31.53785738965662</v>
+        <v>-32.05239166335614</v>
       </c>
       <c r="F25">
-        <v>2.332833801796074</v>
+        <v>1.277168696388363</v>
       </c>
       <c r="G25">
-        <v>-3.466436968838262</v>
+        <v>-6.645441291652047</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.070552801116873</v>
       </c>
       <c r="E26">
-        <v>-31.77430260301911</v>
+        <v>-33.16373579076354</v>
       </c>
       <c r="F26">
-        <v>2.287923069446042</v>
+        <v>0.3627337334017948</v>
       </c>
       <c r="G26">
-        <v>-3.736296088471953</v>
+        <v>-4.905594015124693</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.753226188356217</v>
       </c>
       <c r="E27">
-        <v>-32.26954331320895</v>
+        <v>-33.33004399869523</v>
       </c>
       <c r="F27">
-        <v>1.891684600520839</v>
+        <v>1.247602490653024</v>
       </c>
       <c r="G27">
-        <v>-3.616454339950336</v>
+        <v>-4.625151081401953</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.341267259153619</v>
       </c>
       <c r="E28">
-        <v>-32.01929304683408</v>
+        <v>-32.13060067370561</v>
       </c>
       <c r="F28">
-        <v>2.293274411734312</v>
+        <v>0.5008423914636073</v>
       </c>
       <c r="G28">
-        <v>-2.839207768785786</v>
+        <v>-4.206959658335677</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.857873324263163</v>
       </c>
       <c r="E29">
-        <v>-32.33556167152977</v>
+        <v>-32.92014690965395</v>
       </c>
       <c r="F29">
-        <v>1.778951662342113</v>
+        <v>0.713429571316706</v>
       </c>
       <c r="G29">
-        <v>-3.643134026451322</v>
+        <v>-4.19377044490722</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.330230489080943</v>
       </c>
       <c r="E30">
-        <v>-31.37887625266933</v>
+        <v>-32.82132654985857</v>
       </c>
       <c r="F30">
-        <v>1.632026513449049</v>
+        <v>0.4652921529267803</v>
       </c>
       <c r="G30">
-        <v>-3.31672747846134</v>
+        <v>-5.957066315489232</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.780609472056801</v>
       </c>
       <c r="E31">
-        <v>-30.57850696384266</v>
+        <v>-34.04076308759205</v>
       </c>
       <c r="F31">
-        <v>1.81407825954656</v>
+        <v>0.8616169338243752</v>
       </c>
       <c r="G31">
-        <v>-3.309702500827007</v>
+        <v>-4.892096920961085</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.237400574518266</v>
       </c>
       <c r="E32">
-        <v>-31.88719066731932</v>
+        <v>-31.57252512242234</v>
       </c>
       <c r="F32">
-        <v>1.480017668567424</v>
+        <v>1.032660340103666</v>
       </c>
       <c r="G32">
-        <v>-4.100823568346643</v>
+        <v>-5.529532532911134</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.718540641517928</v>
       </c>
       <c r="E33">
-        <v>-32.02213013579988</v>
+        <v>-31.54714528984635</v>
       </c>
       <c r="F33">
-        <v>1.696605289562923</v>
+        <v>0.625001767822229</v>
       </c>
       <c r="G33">
-        <v>-4.007863449603907</v>
+        <v>-4.695188982830773</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.237782951643661</v>
       </c>
       <c r="E34">
-        <v>-29.47056598465203</v>
+        <v>-30.44625061621165</v>
       </c>
       <c r="F34">
-        <v>2.241879987366471</v>
+        <v>0.7824094661695866</v>
       </c>
       <c r="G34">
-        <v>-3.507136815698062</v>
+        <v>-5.532131311159461</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.806145282628856</v>
       </c>
       <c r="E35">
-        <v>-29.65514884944167</v>
+        <v>-32.49068454866252</v>
       </c>
       <c r="F35">
-        <v>2.309352194187853</v>
+        <v>0.1664056703295551</v>
       </c>
       <c r="G35">
-        <v>-5.049387560622937</v>
+        <v>-6.469936030433125</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.418921383235036</v>
       </c>
       <c r="E36">
-        <v>-30.23286212825921</v>
+        <v>-31.04276385487202</v>
       </c>
       <c r="F36">
-        <v>1.784534225694037</v>
+        <v>1.14830412975497</v>
       </c>
       <c r="G36">
-        <v>-4.13998732207622</v>
+        <v>-6.828792545799043</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.075180667495179</v>
       </c>
       <c r="E37">
-        <v>-29.53067694862984</v>
+        <v>-30.81957801340399</v>
       </c>
       <c r="F37">
-        <v>2.253081539306375</v>
+        <v>0.426047128489233</v>
       </c>
       <c r="G37">
-        <v>-3.914227979571161</v>
+        <v>-5.868522464495886</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.7615212276443933</v>
       </c>
       <c r="E38">
-        <v>-27.70599853858619</v>
+        <v>-30.71926099294907</v>
       </c>
       <c r="F38">
-        <v>2.065285691853565</v>
+        <v>0.7988483335718481</v>
       </c>
       <c r="G38">
-        <v>-5.528181830331111</v>
+        <v>-6.052648386299071</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.4607661281686518</v>
       </c>
       <c r="E39">
-        <v>-26.99617835177989</v>
+        <v>-28.98542377149929</v>
       </c>
       <c r="F39">
-        <v>1.877044823038517</v>
+        <v>1.06417292040908</v>
       </c>
       <c r="G39">
-        <v>-4.368080599186466</v>
+        <v>-5.179005350122022</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.1623558344450382</v>
       </c>
       <c r="E40">
-        <v>-26.62037840777936</v>
+        <v>-26.43711106468894</v>
       </c>
       <c r="F40">
-        <v>2.133573507221398</v>
+        <v>1.131719561408488</v>
       </c>
       <c r="G40">
-        <v>-5.812822535797648</v>
+        <v>-6.286343106461763</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.1552638546674122</v>
       </c>
       <c r="E41">
-        <v>-26.64749038166328</v>
+        <v>-26.3898564384189</v>
       </c>
       <c r="F41">
-        <v>2.013200771706592</v>
+        <v>0.809915270508939</v>
       </c>
       <c r="G41">
-        <v>-5.607002609075619</v>
+        <v>-9.01055792527263</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.5013666543930356</v>
       </c>
       <c r="E42">
-        <v>-27.4730991203717</v>
+        <v>-25.47637719006564</v>
       </c>
       <c r="F42">
-        <v>2.767133474987034</v>
+        <v>1.224543732524225</v>
       </c>
       <c r="G42">
-        <v>-5.668866773567979</v>
+        <v>-6.920713153242446</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.8864748338352539</v>
       </c>
       <c r="E43">
-        <v>-25.47420805101597</v>
+        <v>-25.05663293429468</v>
       </c>
       <c r="F43">
-        <v>2.801173649933489</v>
+        <v>1.676693355088103</v>
       </c>
       <c r="G43">
-        <v>-6.726536415182035</v>
+        <v>-7.473405420478232</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.319905118557315</v>
       </c>
       <c r="E44">
-        <v>-23.31770797229728</v>
+        <v>-25.10346641248201</v>
       </c>
       <c r="F44">
-        <v>2.243745592934859</v>
+        <v>1.136640135687759</v>
       </c>
       <c r="G44">
-        <v>-6.371079830084948</v>
+        <v>-7.595826083974941</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.796059722768831</v>
       </c>
       <c r="E45">
-        <v>-22.97661425309153</v>
+        <v>-25.73588139307519</v>
       </c>
       <c r="F45">
-        <v>2.849296137880032</v>
+        <v>1.191727762250405</v>
       </c>
       <c r="G45">
-        <v>-7.416033666282662</v>
+        <v>-8.201947245669025</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.31838242497191</v>
       </c>
       <c r="E46">
-        <v>-21.94518184226049</v>
+        <v>-21.92888386430688</v>
       </c>
       <c r="F46">
-        <v>2.849259712643977</v>
+        <v>1.262501995905478</v>
       </c>
       <c r="G46">
-        <v>-7.745605095808187</v>
+        <v>-8.518663826865559</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.878202418868487</v>
       </c>
       <c r="E47">
-        <v>-22.71149927078648</v>
+        <v>-23.77771036199643</v>
       </c>
       <c r="F47">
-        <v>2.419052335538513</v>
+        <v>0.8924611902334738</v>
       </c>
       <c r="G47">
-        <v>-6.342943503546683</v>
+        <v>-8.531594817741952</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.466121221144663</v>
       </c>
       <c r="E48">
-        <v>-21.09118409999798</v>
+        <v>-21.88655621775719</v>
       </c>
       <c r="F48">
-        <v>3.035723663421902</v>
+        <v>1.345462846579858</v>
       </c>
       <c r="G48">
-        <v>-7.726784644417431</v>
+        <v>-8.943999407205583</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.077261424766371</v>
       </c>
       <c r="E49">
-        <v>-20.77519171221675</v>
+        <v>-24.1916717564596</v>
       </c>
       <c r="F49">
-        <v>2.585623356312603</v>
+        <v>1.214834031556666</v>
       </c>
       <c r="G49">
-        <v>-7.047146197932753</v>
+        <v>-7.5614957267327</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.692723208670363</v>
       </c>
       <c r="E50">
-        <v>-20.71681515378387</v>
+        <v>-23.23602335814692</v>
       </c>
       <c r="F50">
-        <v>2.592438042866739</v>
+        <v>1.606322966441466</v>
       </c>
       <c r="G50">
-        <v>-7.295112679915243</v>
+        <v>-9.101051687588608</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.308969910876725</v>
       </c>
       <c r="E51">
-        <v>-19.31605398830925</v>
+        <v>-20.98988213644639</v>
       </c>
       <c r="F51">
-        <v>2.761433717397367</v>
+        <v>1.748587268825392</v>
       </c>
       <c r="G51">
-        <v>-8.434370716344636</v>
+        <v>-9.398888227574679</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.915100130631382</v>
       </c>
       <c r="E52">
-        <v>-18.86735919820725</v>
+        <v>-17.65138241461562</v>
       </c>
       <c r="F52">
-        <v>2.754457492839856</v>
+        <v>1.597756701144855</v>
       </c>
       <c r="G52">
-        <v>-8.703243293407624</v>
+        <v>-9.131581538551767</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.499081464232734</v>
       </c>
       <c r="E53">
-        <v>-19.31354068523499</v>
+        <v>-20.07830484717635</v>
       </c>
       <c r="F53">
-        <v>2.760192091959663</v>
+        <v>1.375755973330384</v>
       </c>
       <c r="G53">
-        <v>-9.38361999154756</v>
+        <v>-8.566252918992584</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.058844474364308</v>
       </c>
       <c r="E54">
-        <v>-17.28890976961966</v>
+        <v>-18.81984644891877</v>
       </c>
       <c r="F54">
-        <v>2.808813447269569</v>
+        <v>1.266937956174624</v>
       </c>
       <c r="G54">
-        <v>-9.546177709162393</v>
+        <v>-9.419218287731344</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.581228551580793</v>
       </c>
       <c r="E55">
-        <v>-16.07984796583775</v>
+        <v>-19.11980803871285</v>
       </c>
       <c r="F55">
-        <v>2.62001036285454</v>
+        <v>1.520867778950269</v>
       </c>
       <c r="G55">
-        <v>-9.233903880079561</v>
+        <v>-9.085313354094913</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.064533152301347</v>
       </c>
       <c r="E56">
-        <v>-15.04840649805868</v>
+        <v>-19.65359285541898</v>
       </c>
       <c r="F56">
-        <v>2.863386369409697</v>
+        <v>1.662132762901553</v>
       </c>
       <c r="G56">
-        <v>-9.048569609154541</v>
+        <v>-8.757529619160593</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.503727624365361</v>
       </c>
       <c r="E57">
-        <v>-15.84291367728243</v>
+        <v>-16.61142741570214</v>
       </c>
       <c r="F57">
-        <v>3.034746516872076</v>
+        <v>1.581740683222015</v>
       </c>
       <c r="G57">
-        <v>-9.645464280430676</v>
+        <v>-10.97668429995471</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.890477607816932</v>
       </c>
       <c r="E58">
-        <v>-15.0725659068896</v>
+        <v>-18.12420491423049</v>
       </c>
       <c r="F58">
-        <v>2.576773607657127</v>
+        <v>1.572540935559228</v>
       </c>
       <c r="G58">
-        <v>-10.29919108697948</v>
+        <v>-8.689762751971713</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.225355462102028</v>
       </c>
       <c r="E59">
-        <v>-15.14152550907841</v>
+        <v>-17.61610107362186</v>
       </c>
       <c r="F59">
-        <v>3.080876702776997</v>
+        <v>1.047922514010756</v>
       </c>
       <c r="G59">
-        <v>-11.15663893437841</v>
+        <v>-10.69014334134863</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.500183745158997</v>
       </c>
       <c r="E60">
-        <v>-14.33573337262755</v>
+        <v>-16.6496613217489</v>
       </c>
       <c r="F60">
-        <v>3.144079238450354</v>
+        <v>1.525316408866739</v>
       </c>
       <c r="G60">
-        <v>-10.19329335626927</v>
+        <v>-10.16120423835712</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.713186715096105</v>
       </c>
       <c r="E61">
-        <v>-15.36753711832723</v>
+        <v>-16.71037004429573</v>
       </c>
       <c r="F61">
-        <v>2.746021091428311</v>
+        <v>0.8845363258326149</v>
       </c>
       <c r="G61">
-        <v>-11.22774283147088</v>
+        <v>-10.88966661045497</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.861721631180078</v>
       </c>
       <c r="E62">
-        <v>-14.86259868104996</v>
+        <v>-15.23991113536905</v>
       </c>
       <c r="F62">
-        <v>2.990629221185679</v>
+        <v>0.9343644650500862</v>
       </c>
       <c r="G62">
-        <v>-11.00785639675249</v>
+        <v>-10.68390958409818</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.941295218034211</v>
       </c>
       <c r="E63">
-        <v>-13.94677821163474</v>
+        <v>-16.0599860788401</v>
       </c>
       <c r="F63">
-        <v>2.920434623895657</v>
+        <v>1.21823583186303</v>
       </c>
       <c r="G63">
-        <v>-10.83598280399015</v>
+        <v>-10.34584991580997</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.956052155818684</v>
       </c>
       <c r="E64">
-        <v>-13.48705205885005</v>
+        <v>-14.32509145870953</v>
       </c>
       <c r="F64">
-        <v>2.30748500491355</v>
+        <v>1.257326444973822</v>
       </c>
       <c r="G64">
-        <v>-11.43083486866855</v>
+        <v>-12.41034253010041</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.903692812020536</v>
       </c>
       <c r="E65">
-        <v>-12.8498776520748</v>
+        <v>-12.88094298376742</v>
       </c>
       <c r="F65">
-        <v>2.693931420163592</v>
+        <v>1.523210079999204</v>
       </c>
       <c r="G65">
-        <v>-11.545899499977</v>
+        <v>-11.11541933186895</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.789223348575636</v>
       </c>
       <c r="E66">
-        <v>-14.07228034028331</v>
+        <v>-15.80431749331505</v>
       </c>
       <c r="F66">
-        <v>2.339067268279244</v>
+        <v>0.802563707649469</v>
       </c>
       <c r="G66">
-        <v>-10.51442289466966</v>
+        <v>-11.33981804015737</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.61550129257369</v>
       </c>
       <c r="E67">
-        <v>-13.06608511509701</v>
+        <v>-15.44487892590423</v>
       </c>
       <c r="F67">
-        <v>2.61615245524453</v>
+        <v>0.3945947290086056</v>
       </c>
       <c r="G67">
-        <v>-11.40605212476156</v>
+        <v>-11.05165160369151</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.386661754952693</v>
       </c>
       <c r="E68">
-        <v>-12.32032695856585</v>
+        <v>-13.06614851373312</v>
       </c>
       <c r="F68">
-        <v>2.241781797599714</v>
+        <v>0.6222746262358424</v>
       </c>
       <c r="G68">
-        <v>-11.27774531129603</v>
+        <v>-11.49160986367849</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.112573961633439</v>
       </c>
       <c r="E69">
-        <v>-13.96397282744186</v>
+        <v>-16.64302257885365</v>
       </c>
       <c r="F69">
-        <v>2.188974707555301</v>
+        <v>0.7767318804627362</v>
       </c>
       <c r="G69">
-        <v>-11.88551181412313</v>
+        <v>-12.1312933360497</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.794688401238167</v>
       </c>
       <c r="E70">
-        <v>-12.92530844362057</v>
+        <v>-15.78877124204672</v>
       </c>
       <c r="F70">
-        <v>1.850131324711539</v>
+        <v>0.5796713534046057</v>
       </c>
       <c r="G70">
-        <v>-11.14831953343822</v>
+        <v>-10.69368893562119</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.44561982187281</v>
       </c>
       <c r="E71">
-        <v>-12.84908969759747</v>
+        <v>-14.80290886515486</v>
       </c>
       <c r="F71">
-        <v>1.457841034633526</v>
+        <v>0.08321755785630955</v>
       </c>
       <c r="G71">
-        <v>-12.07074014759089</v>
+        <v>-11.30587170619768</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.071186855324243</v>
       </c>
       <c r="E72">
-        <v>-12.86272040436055</v>
+        <v>-13.86290634453868</v>
       </c>
       <c r="F72">
-        <v>1.674935441521965</v>
+        <v>0.727830209205797</v>
       </c>
       <c r="G72">
-        <v>-11.74833273861235</v>
+        <v>-12.1710993356139</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.678360295596925</v>
       </c>
       <c r="E73">
-        <v>-13.07715270557176</v>
+        <v>-15.62101392243257</v>
       </c>
       <c r="F73">
-        <v>1.564304081093027</v>
+        <v>0.3896020961101828</v>
       </c>
       <c r="G73">
-        <v>-11.46572801865247</v>
+        <v>-12.11634953348543</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.278108862350614</v>
       </c>
       <c r="E74">
-        <v>-12.51684461660271</v>
+        <v>-13.07639192193847</v>
       </c>
       <c r="F74">
-        <v>2.313810326339815</v>
+        <v>0.5229984372206051</v>
       </c>
       <c r="G74">
-        <v>-11.79286619720663</v>
+        <v>-11.81360345446462</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.871513810913569</v>
       </c>
       <c r="E75">
-        <v>-12.41108663462757</v>
+        <v>-17.47099065252007</v>
       </c>
       <c r="F75">
-        <v>1.638226722107994</v>
+        <v>0.237848227880944</v>
       </c>
       <c r="G75">
-        <v>-10.83553919088788</v>
+        <v>-10.33939766255393</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.469145779646702</v>
       </c>
       <c r="E76">
-        <v>-12.71621974173841</v>
+        <v>-15.46222750982762</v>
       </c>
       <c r="F76">
-        <v>1.846140385804631</v>
+        <v>0.5215081699541766</v>
       </c>
       <c r="G76">
-        <v>-10.1124101076538</v>
+        <v>-9.596190120624163</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.075289888527354</v>
       </c>
       <c r="E77">
-        <v>-14.02993457983759</v>
+        <v>-15.00305835934587</v>
       </c>
       <c r="F77">
-        <v>1.378175875969175</v>
+        <v>0.7562339747992034</v>
       </c>
       <c r="G77">
-        <v>-11.11903775814337</v>
+        <v>-10.6904446009927</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.691740292410272</v>
       </c>
       <c r="E78">
-        <v>-14.12571633357383</v>
+        <v>-15.45677522712238</v>
       </c>
       <c r="F78">
-        <v>1.56283756941533</v>
+        <v>-0.09387718872587578</v>
       </c>
       <c r="G78">
-        <v>-9.511665271915492</v>
+        <v>-11.03635688330007</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.326163801695031</v>
       </c>
       <c r="E79">
-        <v>-13.47710752992921</v>
+        <v>-16.2809665534664</v>
       </c>
       <c r="F79">
-        <v>0.9490375003566327</v>
+        <v>-0.1027530685289562</v>
       </c>
       <c r="G79">
-        <v>-10.0566373469537</v>
+        <v>-10.36313096352496</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.975608245088141</v>
       </c>
       <c r="E80">
-        <v>-14.58947282822534</v>
+        <v>-17.42691954347742</v>
       </c>
       <c r="F80">
-        <v>1.746403338368001</v>
+        <v>-0.6480752775099674</v>
       </c>
       <c r="G80">
-        <v>-10.30688810535828</v>
+        <v>-11.60385391018748</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.64308293642789</v>
       </c>
       <c r="E81">
-        <v>-15.81409899717162</v>
+        <v>-16.82851793115585</v>
       </c>
       <c r="F81">
-        <v>1.599136108997202</v>
+        <v>0.241295163805898</v>
       </c>
       <c r="G81">
-        <v>-10.27683166240724</v>
+        <v>-11.09824422161121</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.328003149812352</v>
       </c>
       <c r="E82">
-        <v>-17.39086836190236</v>
+        <v>-17.29612362871388</v>
       </c>
       <c r="F82">
-        <v>1.97212735878967</v>
+        <v>-0.05178070178757983</v>
       </c>
       <c r="G82">
-        <v>-9.743122063293637</v>
+        <v>-9.083959340969351</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.023089248723364</v>
       </c>
       <c r="E83">
-        <v>-17.45687992751217</v>
+        <v>-16.39600790715726</v>
       </c>
       <c r="F83">
-        <v>1.568195246527262</v>
+        <v>0.05135656224949875</v>
       </c>
       <c r="G83">
-        <v>-9.585328220709815</v>
+        <v>-7.902518333278564</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.730397459836304</v>
       </c>
       <c r="E84">
-        <v>-18.17689823778374</v>
+        <v>-18.9168644760591</v>
       </c>
       <c r="F84">
-        <v>1.566267876428172</v>
+        <v>0.3798179609645979</v>
       </c>
       <c r="G84">
-        <v>-9.0564818129934</v>
+        <v>-9.612881891233169</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.442769030621238</v>
       </c>
       <c r="E85">
-        <v>-19.09944349110036</v>
+        <v>-20.6678306504429</v>
       </c>
       <c r="F85">
-        <v>0.9461583230023637</v>
+        <v>0.6006665427255865</v>
       </c>
       <c r="G85">
-        <v>-7.79142635661724</v>
+        <v>-10.34917701407693</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.158796967818049</v>
       </c>
       <c r="E86">
-        <v>-20.97732014954912</v>
+        <v>-21.83635355490815</v>
       </c>
       <c r="F86">
-        <v>1.209758254097683</v>
+        <v>0.7266836061230189</v>
       </c>
       <c r="G86">
-        <v>-7.840131102590998</v>
+        <v>-9.203930200766999</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.878900749912674</v>
       </c>
       <c r="E87">
-        <v>-21.40337256961276</v>
+        <v>-23.80818699206806</v>
       </c>
       <c r="F87">
-        <v>1.460724963105541</v>
+        <v>-0.1329313766006125</v>
       </c>
       <c r="G87">
-        <v>-7.81591115142569</v>
+        <v>-8.920107200048662</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.599566491950708</v>
       </c>
       <c r="E88">
-        <v>-22.08804614025447</v>
+        <v>-21.902980992983</v>
       </c>
       <c r="F88">
-        <v>1.27384291396594</v>
+        <v>-0.2799729278784612</v>
       </c>
       <c r="G88">
-        <v>-6.883919750118987</v>
+        <v>-7.702190601606185</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.327577010879879</v>
       </c>
       <c r="E89">
-        <v>-24.23726443276883</v>
+        <v>-25.02520985315546</v>
       </c>
       <c r="F89">
-        <v>0.9730021382690623</v>
+        <v>0.001614735004418865</v>
       </c>
       <c r="G89">
-        <v>-7.386182477155054</v>
+        <v>-7.831285324910065</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.064974699221636</v>
       </c>
       <c r="E90">
-        <v>-24.5561188161229</v>
+        <v>-26.9000660194411</v>
       </c>
       <c r="F90">
-        <v>1.070303446007747</v>
+        <v>-0.08014804214493121</v>
       </c>
       <c r="G90">
-        <v>-7.204072677585286</v>
+        <v>-9.355066536271346</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.815988423002262</v>
       </c>
       <c r="E91">
-        <v>-25.62942602610288</v>
+        <v>-26.14051413108256</v>
       </c>
       <c r="F91">
-        <v>1.002338706646663</v>
+        <v>-0.309073524074661</v>
       </c>
       <c r="G91">
-        <v>-7.277732315834069</v>
+        <v>-8.583904747807978</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.587100281691876</v>
       </c>
       <c r="E92">
-        <v>-27.25033895546039</v>
+        <v>-30.66673975140811</v>
       </c>
       <c r="F92">
-        <v>1.06508988613412</v>
+        <v>-0.6269114235089923</v>
       </c>
       <c r="G92">
-        <v>-6.792929405972118</v>
+        <v>-8.79193611895024</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.378138211560145</v>
       </c>
       <c r="E93">
-        <v>-29.04879070828862</v>
+        <v>-30.81789794954715</v>
       </c>
       <c r="F93">
-        <v>0.7091028867557255</v>
+        <v>-0.5755217502588977</v>
       </c>
       <c r="G93">
-        <v>-7.562220736205799</v>
+        <v>-7.260987576496436</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.192217285269991</v>
       </c>
       <c r="E94">
-        <v>-29.96637501832983</v>
+        <v>-33.25609854662399</v>
       </c>
       <c r="F94">
-        <v>0.57512770113321</v>
+        <v>-0.5668683811369366</v>
       </c>
       <c r="G94">
-        <v>-7.163756854008041</v>
+        <v>-8.762571580016903</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.027111084850976</v>
       </c>
       <c r="E95">
-        <v>-32.02365396730346</v>
+        <v>-33.63288116948418</v>
       </c>
       <c r="F95">
-        <v>0.08835905911078372</v>
+        <v>-0.8422336634780551</v>
       </c>
       <c r="G95">
-        <v>-6.477288752075846</v>
+        <v>-7.010680538817681</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.8771836989804183</v>
       </c>
       <c r="E96">
-        <v>-34.6323561392431</v>
+        <v>-37.38451583927172</v>
       </c>
       <c r="F96">
-        <v>0.1696886926922611</v>
+        <v>-0.7095610759709885</v>
       </c>
       <c r="G96">
-        <v>-6.252681479418453</v>
+        <v>-7.170626236002029</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.7402313033653272</v>
       </c>
       <c r="E97">
-        <v>-37.24344934545879</v>
+        <v>-37.67556765645571</v>
       </c>
       <c r="F97">
-        <v>-0.08993692840826244</v>
+        <v>-0.2867947411092166</v>
       </c>
       <c r="G97">
-        <v>-6.762733920108426</v>
+        <v>-8.078920752338629</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.6051411611806168</v>
       </c>
       <c r="E98">
-        <v>-37.85506504493474</v>
+        <v>-40.74311972145955</v>
       </c>
       <c r="F98">
-        <v>-0.2164346465510306</v>
+        <v>-1.03980651939983</v>
       </c>
       <c r="G98">
-        <v>-6.237601944487073</v>
+        <v>-8.472494958774885</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.468317271403602</v>
       </c>
       <c r="E99">
-        <v>-40.69456995162331</v>
+        <v>-42.7618568281539</v>
       </c>
       <c r="F99">
-        <v>-0.3749129300972252</v>
+        <v>-0.7089402632521362</v>
       </c>
       <c r="G99">
-        <v>-6.682264489685361</v>
+        <v>-8.025971886983525</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.3186308119183408</v>
       </c>
       <c r="E100">
-        <v>-43.57800105618629</v>
+        <v>-43.45820933326139</v>
       </c>
       <c r="F100">
-        <v>-0.7804208297454958</v>
+        <v>-1.717700750562278</v>
       </c>
       <c r="G100">
-        <v>-7.613971184075687</v>
+        <v>-9.347412554984551</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.1560489849979293</v>
       </c>
       <c r="E101">
-        <v>-44.297512177369</v>
+        <v>-46.63014498837903</v>
       </c>
       <c r="F101">
-        <v>-0.641756290907364</v>
+        <v>-1.587409264899074</v>
       </c>
       <c r="G101">
-        <v>-6.070657754032705</v>
+        <v>-8.436873488772326</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.03072014160584146</v>
       </c>
       <c r="E102">
-        <v>-46.07629223910791</v>
+        <v>-47.0969468818007</v>
       </c>
       <c r="F102">
-        <v>-0.335340078535182</v>
+        <v>-1.334414620466496</v>
       </c>
       <c r="G102">
-        <v>-7.076060502672747</v>
+        <v>-8.961750552387155</v>
       </c>
     </row>
   </sheetData>
